--- a/output/pdf_financials_xlsx/CVG.xlsx
+++ b/output/pdf_financials_xlsx/CVG.xlsx
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>11.586</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>14.375</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>14.827</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>19.325</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1083,34 +1083,34 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>20.266</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>51.245</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>275.975</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>80.39700000000001</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>20.561</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>43.486</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>160.941</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>32.778</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>128.296</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>29.654</v>
       </c>
     </row>
     <row r="13">
@@ -2154,16 +2154,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>31.118</v>
+        <v>19.532</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>7.016</v>
+        <v>-7.359</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>22.63</v>
+        <v>7.803</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>26.886</v>
+        <v>7.561</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>41.774</v>
@@ -2178,34 +2178,34 @@
         <v>43.227</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>59.334</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>136.694</v>
+        <v>85.449</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>137.878</v>
+        <v>-138.097</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>79.28400000000001</v>
+        <v>-1.113</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>116.789</v>
+        <v>96.22799999999999</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>375.013</v>
+        <v>331.527</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>63.684</v>
+        <v>-97.25700000000001</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-3.173</v>
+        <v>-35.951</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>138.541</v>
+        <v>10.245</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>130.945</v>
+        <v>101.291</v>
       </c>
     </row>
     <row r="28">
@@ -2276,16 +2276,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>31.118</v>
+        <v>19.532</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>7.016</v>
+        <v>-7.359</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>22.63</v>
+        <v>7.803</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>26.886</v>
+        <v>7.561</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>41.774</v>
@@ -2300,34 +2300,34 @@
         <v>43.227</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>59.334</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>136.694</v>
+        <v>85.449</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>137.878</v>
+        <v>-138.097</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>79.28400000000001</v>
+        <v>-1.113</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>116.789</v>
+        <v>96.22799999999999</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>375.013</v>
+        <v>331.527</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>63.684</v>
+        <v>-97.25700000000001</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.173</v>
+        <v>-35.951</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>138.541</v>
+        <v>10.245</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>130.945</v>
+        <v>101.291</v>
       </c>
     </row>
     <row r="30">
@@ -2371,34 +2371,34 @@
         <v>56.93981585152206</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>60.5461321974595</v>
+        <v>45.13120864075454</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>65.65860828381904</v>
+        <v>41.04395525219872</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>67.5187432360301</v>
+        <v>-67.62598735596723</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>61.31881390276725</v>
+        <v>-0.8608021779145849</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>65.71406064493623</v>
+        <v>54.14493340760622</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>89.06466345411667</v>
+        <v>78.73684560522685</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>48.91882964749622</v>
+        <v>-74.70791117119747</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-8.657335406946604</v>
+        <v>-98.09009303975334</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>78.50193505249857</v>
+        <v>5.805157495707753</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>66.08777720578587</v>
+        <v>51.12144061209863</v>
       </c>
     </row>
     <row r="31">
@@ -46494,7 +46494,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -53096,7 +53096,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -53202,7 +53202,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -64162,7 +64162,7 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -65398,7 +65398,7 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E557" s="5" t="n">

--- a/output/pdf_financials_xlsx/CVG.xlsx
+++ b/output/pdf_financials_xlsx/CVG.xlsx
@@ -7173,13 +7173,13 @@
         <v>1.516</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>1.225</v>
+        <v>3.811</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>8.766999999999999</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>4.608</v>
       </c>
       <c r="J107" s="3" t="n">
         <v>12.263</v>
@@ -30116,7 +30116,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -33412,7 +33416,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -36994,7 +37002,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -38048,7 +38060,11 @@
           <t>Share‐based compensation expense</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -40562,7 +40578,11 @@
           <t>Future income tax expense</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -41816,7 +41836,11 @@
           <t>Future income tax expense</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
